--- a/public_html/assets/archivo/corte/10-NUTRICION/10-NUTRICION_33-2024_10.xlsx
+++ b/public_html/assets/archivo/corte/10-NUTRICION/10-NUTRICION_33-2024_10.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="44">
   <si>
     <t>PAGO</t>
   </si>
@@ -52,58 +52,55 @@
     <t>DESCRIPCIÓN</t>
   </si>
   <si>
+    <t xml:space="preserve">RENE JAVIER MEDRANO LOPEZ  </t>
+  </si>
+  <si>
+    <t>012650028495052889</t>
+  </si>
+  <si>
+    <t>PAGO SEMANA 33-2024</t>
+  </si>
+  <si>
+    <t>BBVA MEXICO</t>
+  </si>
+  <si>
+    <t>DEL 12 DE AGOSTO AL 18 DE AGOSTO</t>
+  </si>
+  <si>
     <t xml:space="preserve">HECTOR JAVIER ARMANDO RODRIGUEZ VALDES  </t>
   </si>
   <si>
-    <t>'002420903527668862'</t>
-  </si>
-  <si>
-    <t>PAGO SEMANA 33-2024</t>
+    <t>002420903527668862</t>
   </si>
   <si>
     <t>BANAMEX</t>
   </si>
   <si>
-    <t>DEL 12 DE AGOSTO AL 18 DE AGOSTO</t>
-  </si>
-  <si>
     <t>GERARDO DANIEL   HERMIDA AMADOR</t>
   </si>
   <si>
-    <t>'127290013759479947'</t>
-  </si>
-  <si>
     <t>AZTECA</t>
   </si>
   <si>
-    <t xml:space="preserve">SOFIA BARROSO RUIZ  </t>
-  </si>
-  <si>
-    <t>'012261004726315475'</t>
-  </si>
-  <si>
-    <t>BBVA MEXICO</t>
+    <t xml:space="preserve">MA GUADALUPE VAZQUEZ FLORES  </t>
   </si>
   <si>
     <t>MARIA DE LA LUZ  MUÑOZ  CASTELLANOS</t>
   </si>
   <si>
-    <t>'012320029389721173'</t>
+    <t>012320029389721173</t>
   </si>
   <si>
     <t xml:space="preserve">MANUEL DE JESUS CASTALDI PEREZ  </t>
   </si>
   <si>
-    <t>'127131013606487141'</t>
-  </si>
-  <si>
     <t>BENEFICIARIO</t>
   </si>
   <si>
     <t>IMPORTE</t>
   </si>
   <si>
-    <t>RETENCIÓN DE IVA 10.66%</t>
+    <t>RET DE IVA 10.66%</t>
   </si>
   <si>
     <t>IVA 16%</t>
@@ -115,32 +112,54 @@
     <t xml:space="preserve">LUIS ALBERTO LIN SALINAS  </t>
   </si>
   <si>
-    <t>LISL720802GW9</t>
-  </si>
-  <si>
     <t>012180015558104539</t>
   </si>
   <si>
+    <t>PAGO DE COMISIONES</t>
+  </si>
+  <si>
     <t>IGNACIO  ALCOCER  CARVAJAL</t>
   </si>
   <si>
-    <t>AOCI730717A95</t>
-  </si>
-  <si>
     <t>012261011384032604</t>
   </si>
   <si>
-    <t>RFC</t>
+    <t>EUGENIA  ALCOCER  CARVAJAL</t>
+  </si>
+  <si>
+    <t>012261015099257013</t>
+  </si>
+  <si>
+    <t>CODIGO SAT</t>
+  </si>
+  <si>
+    <t>CONCEPTO FACTURA</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>DESC. BONIFICACIÓN PRONTO PAGO BENELEIT</t>
+  </si>
+  <si>
+    <t>NETO</t>
+  </si>
+  <si>
+    <t>IVA</t>
+  </si>
+  <si>
+    <t>RET 1.25%</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="#"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <b val="0"/>
       <i val="0"/>
@@ -150,13 +169,34 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="11"/>
+      <color rgb="FFffffff"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF009779"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF192b5a"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -171,10 +211,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="11">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="0" numFmtId="164" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="0" numFmtId="49" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="165" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="164" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="165" fillId="2" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="164" fillId="3" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="164" fillId="3" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -474,16 +534,16 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="5.856" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="6.998" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="9.283" bestFit="true" customWidth="true" style="2"/>
+    <col min="2" max="2" width="9.283" bestFit="true" customWidth="true" style="2"/>
     <col min="3" max="3" width="48.274" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="24.708" bestFit="true" customWidth="true" style="2"/>
-    <col min="5" max="5" width="15.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="23.423" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="13.997" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="24.565" bestFit="true" customWidth="true" style="3"/>
+    <col min="5" max="5" width="17.567" bestFit="true" customWidth="true" style="2"/>
+    <col min="6" max="6" width="25.708" bestFit="true" customWidth="true" style="2"/>
+    <col min="7" max="7" width="16.282" bestFit="true" customWidth="true" style="2"/>
     <col min="8" max="8" width="11.711" bestFit="true" customWidth="true" style="1"/>
     <col min="9" max="9" width="9.283" bestFit="true" customWidth="true" style="1"/>
     <col min="10" max="10" width="11.711" bestFit="true" customWidth="true" style="1"/>
@@ -491,212 +551,247 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2">
-        <v>5866</v>
-      </c>
-      <c r="B2">
-        <v>11101</v>
+      <c r="A2" s="2">
+        <v>11428</v>
+      </c>
+      <c r="B2" s="2">
+        <v>92</v>
       </c>
       <c r="C2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="2">
         <v>30</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H2" s="1">
-        <v>600.0</v>
+        <v>2531.95</v>
       </c>
       <c r="I2" s="1">
-        <v>30.7</v>
+        <v>202.45</v>
       </c>
       <c r="J2" s="1">
-        <v>569.3</v>
+        <v>2329.5</v>
       </c>
       <c r="K2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3">
-        <v>5864</v>
-      </c>
-      <c r="B3">
-        <v>17042</v>
+      <c r="A3" s="2">
+        <v>11431</v>
+      </c>
+      <c r="B3" s="2">
+        <v>11101</v>
       </c>
       <c r="C3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="2">
         <v>30</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="2" t="s">
         <v>18</v>
       </c>
       <c r="H3" s="1">
-        <v>75.0</v>
+        <v>675.0</v>
       </c>
       <c r="I3" s="1">
-        <v>1.44</v>
+        <v>35.5</v>
       </c>
       <c r="J3" s="1">
-        <v>73.56</v>
+        <v>639.5</v>
       </c>
       <c r="K3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4">
-        <v>5869</v>
-      </c>
-      <c r="B4">
-        <v>28842</v>
+      <c r="A4" s="2">
+        <v>11429</v>
+      </c>
+      <c r="B4" s="2">
+        <v>17042</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3">
+        <v>127290013759479947</v>
+      </c>
+      <c r="E4" s="2">
+        <v>30</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E4">
-        <v>30</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" t="s">
-        <v>21</v>
-      </c>
       <c r="H4" s="1">
-        <v>2836.0</v>
+        <v>75.0</v>
       </c>
       <c r="I4" s="1">
-        <v>249.58</v>
+        <v>1.44</v>
       </c>
       <c r="J4" s="1">
-        <v>2586.42</v>
+        <v>73.56</v>
       </c>
       <c r="K4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5">
-        <v>5884</v>
-      </c>
-      <c r="B5">
-        <v>33949</v>
+      <c r="A5" s="2">
+        <v>11432</v>
+      </c>
+      <c r="B5" s="2">
+        <v>25919</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5">
+        <v>21</v>
+      </c>
+      <c r="D5" s="3">
+        <v>127528013932219641</v>
+      </c>
+      <c r="E5" s="2">
         <v>30</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G5" t="s">
-        <v>21</v>
+      <c r="G5" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="H5" s="1">
-        <v>325.0</v>
+        <v>31.35</v>
       </c>
       <c r="I5" s="1">
-        <v>13.1</v>
+        <v>0.6</v>
       </c>
       <c r="J5" s="1">
-        <v>311.9</v>
+        <v>30.75</v>
       </c>
       <c r="K5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6">
-        <v>5891</v>
-      </c>
-      <c r="B6">
+      <c r="A6" s="2">
+        <v>11452</v>
+      </c>
+      <c r="B6" s="2">
+        <v>33949</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="2">
+        <v>30</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="1">
+        <v>425.0</v>
+      </c>
+      <c r="I6" s="1">
+        <v>19.5</v>
+      </c>
+      <c r="J6" s="1">
+        <v>405.5</v>
+      </c>
+      <c r="K6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="2">
+        <v>11459</v>
+      </c>
+      <c r="B7" s="2">
         <v>46264</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C7" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6">
+      <c r="D7" s="3">
+        <v>127131013606487141</v>
+      </c>
+      <c r="E7" s="2">
         <v>30</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="1">
+      <c r="G7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="1">
         <v>450.0</v>
       </c>
-      <c r="I6" s="1">
+      <c r="I7" s="1">
         <v>21.1</v>
       </c>
-      <c r="J6" s="1">
+      <c r="J7" s="1">
         <v>428.9</v>
       </c>
-      <c r="K6" t="s">
+      <c r="K7" t="s">
         <v>15</v>
       </c>
     </row>
@@ -712,133 +807,186 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="5.856" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="6.998" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="9.283" bestFit="true" customWidth="true" style="2"/>
+    <col min="2" max="2" width="9.283" bestFit="true" customWidth="true" style="2"/>
     <col min="3" max="3" width="31.707" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="16.425" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="22.28" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="19.995" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="23.423" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="13.997" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="28.136" bestFit="true" customWidth="true" style="1"/>
+    <col min="4" max="4" width="23.423" bestFit="true" customWidth="true" style="3"/>
+    <col min="5" max="5" width="17.567" bestFit="true" customWidth="true" style="3"/>
+    <col min="6" max="6" width="25.708" bestFit="true" customWidth="true" style="2"/>
+    <col min="7" max="7" width="12.854" bestFit="true" customWidth="true" style="4"/>
+    <col min="8" max="8" width="11.711" bestFit="true" customWidth="true" style="1"/>
+    <col min="9" max="9" width="21.138" bestFit="true" customWidth="true" style="1"/>
     <col min="10" max="10" width="9.283" bestFit="true" customWidth="true" style="1"/>
-    <col min="11" max="11" width="11.711" bestFit="true" customWidth="true" style="1"/>
+    <col min="11" max="11" width="18.71" bestFit="true" customWidth="true" style="0"/>
     <col min="12" max="12" width="38.848" bestFit="true" customWidth="true" style="0"/>
     <col min="13" max="13" width="23.423" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="I1" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="2">
+        <v>11440</v>
+      </c>
+      <c r="B2" s="2">
+        <v>15862</v>
+      </c>
+      <c r="C2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2">
-        <v>5875</v>
-      </c>
-      <c r="B2">
-        <v>15862</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="D2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F2">
+      <c r="E2" s="3">
         <v>30</v>
       </c>
-      <c r="G2" t="s">
+      <c r="F2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H2" t="s">
-        <v>21</v>
+      <c r="G2" s="4">
+        <v>355.60344827586</v>
+      </c>
+      <c r="H2" s="1">
+        <v>412.5</v>
       </c>
       <c r="I2" s="1">
-        <v>312.5</v>
-      </c>
-      <c r="K2" s="1">
-        <v>312.5</v>
+        <v>37.907327586207</v>
+      </c>
+      <c r="J2" s="1">
+        <v>56.896551724138</v>
+      </c>
+      <c r="K2">
+        <v>374.59267241379</v>
       </c>
       <c r="L2" t="s">
         <v>15</v>
       </c>
+      <c r="M2" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3">
-        <v>5868</v>
-      </c>
-      <c r="B3">
+      <c r="A3" s="2">
+        <v>11435</v>
+      </c>
+      <c r="B3" s="2">
         <v>32605</v>
       </c>
       <c r="C3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3">
+      <c r="E3" s="3">
         <v>30</v>
       </c>
-      <c r="G3" t="s">
+      <c r="F3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H3" t="s">
-        <v>21</v>
+      <c r="G3" s="4">
+        <v>752.37068965517</v>
+      </c>
+      <c r="H3" s="1">
+        <v>872.75</v>
       </c>
       <c r="I3" s="1">
-        <v>1122.25</v>
-      </c>
-      <c r="K3" s="1">
-        <v>1122.25</v>
+        <v>80.202715517241</v>
+      </c>
+      <c r="J3" s="1">
+        <v>120.37931034483</v>
+      </c>
+      <c r="K3">
+        <v>792.54728448276</v>
       </c>
       <c r="L3" t="s">
         <v>15</v>
+      </c>
+      <c r="M3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="2">
+        <v>11434</v>
+      </c>
+      <c r="B4" s="2">
+        <v>32614</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="3">
+        <v>30</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="4">
+        <v>931.03448275862</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1080.0</v>
+      </c>
+      <c r="I4" s="1">
+        <v>99.248275862069</v>
+      </c>
+      <c r="J4" s="1">
+        <v>148.96551724138</v>
+      </c>
+      <c r="K4">
+        <v>980.75172413793</v>
+      </c>
+      <c r="L4" t="s">
+        <v>15</v>
+      </c>
+      <c r="M4" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -853,58 +1001,74 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="5.856" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="3.428" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="6.998" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="4.57" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="19.995" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="3.428" bestFit="true" customWidth="true" style="0"/>
     <col min="5" max="5" width="6.998" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="15.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="19.995" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="6.998" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="10.569" bestFit="true" customWidth="true" style="1"/>
-    <col min="10" max="10" width="4.57" bestFit="true" customWidth="true" style="1"/>
-    <col min="11" max="11" width="6.998" bestFit="true" customWidth="true" style="1"/>
-    <col min="12" max="12" width="13.997" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="6.998" bestFit="true" customWidth="true" style="0"/>
+    <col min="7" max="7" width="15.282" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="19.995" bestFit="true" customWidth="true" style="0"/>
+    <col min="9" max="9" width="47.131" bestFit="true" customWidth="true" style="1"/>
+    <col min="10" max="10" width="5.856" bestFit="true" customWidth="true" style="1"/>
+    <col min="11" max="11" width="9.283" bestFit="true" customWidth="true" style="1"/>
+    <col min="12" max="12" width="10.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="13" max="13" width="4.57" bestFit="true" customWidth="true" style="0"/>
+    <col min="14" max="14" width="11.711" bestFit="true" customWidth="true" style="0"/>
+    <col min="15" max="15" width="6.998" bestFit="true" customWidth="true" style="0"/>
+    <col min="16" max="16" width="13.997" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="C1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
-        <v>6</v>
-      </c>
       <c r="I1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N1" t="s">
+        <v>43</v>
+      </c>
+      <c r="O1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" t="s">
+      <c r="P1" t="s">
         <v>10</v>
       </c>
     </row>
